--- a/data/memories/memory_01/locales/es/documents/director/Employee_Registry_Current.xlsx
+++ b/data/memories/memory_01/locales/es/documents/director/Employee_Registry_Current.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Employee Registry Current</t>
+          <t>Registro de Empleados Actual</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,31 +469,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Current Employee Registry</t>
+          <t>Registro de empleados actual</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Posición</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reception</t>
+          <t>Recepción</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reception</t>
+          <t>Recepción</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HORA</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finanzas</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Administración</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Administración</t>
         </is>
       </c>
     </row>
